--- a/artfynd/A 239-2021 artfynd.xlsx
+++ b/artfynd/A 239-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 239-2021 artfynd.xlsx
+++ b/artfynd/A 239-2021 artfynd.xlsx
@@ -22191,7 +22191,7 @@
         <v>121306885</v>
       </c>
       <c r="B185" t="n">
-        <v>74637</v>
+        <v>74640</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>

--- a/artfynd/A 239-2021 artfynd.xlsx
+++ b/artfynd/A 239-2021 artfynd.xlsx
@@ -22191,7 +22191,7 @@
         <v>121306885</v>
       </c>
       <c r="B185" t="n">
-        <v>74640</v>
+        <v>74642</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>

--- a/artfynd/A 239-2021 artfynd.xlsx
+++ b/artfynd/A 239-2021 artfynd.xlsx
@@ -22191,7 +22191,7 @@
         <v>121306885</v>
       </c>
       <c r="B185" t="n">
-        <v>74642</v>
+        <v>74645</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>

--- a/artfynd/A 239-2021 artfynd.xlsx
+++ b/artfynd/A 239-2021 artfynd.xlsx
@@ -22191,7 +22191,7 @@
         <v>121306885</v>
       </c>
       <c r="B185" t="n">
-        <v>74645</v>
+        <v>74646</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>

--- a/artfynd/A 239-2021 artfynd.xlsx
+++ b/artfynd/A 239-2021 artfynd.xlsx
@@ -22191,7 +22191,7 @@
         <v>121306885</v>
       </c>
       <c r="B185" t="n">
-        <v>74646</v>
+        <v>74647</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>

--- a/artfynd/A 239-2021 artfynd.xlsx
+++ b/artfynd/A 239-2021 artfynd.xlsx
@@ -22191,7 +22191,7 @@
         <v>121306885</v>
       </c>
       <c r="B185" t="n">
-        <v>74647</v>
+        <v>74654</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
